--- a/R Markdown/resultados/Produtos_Cesta_2026/tabelas/Produto5_distancia_marco_5b.xlsx
+++ b/R Markdown/resultados/Produtos_Cesta_2026/tabelas/Produto5_distancia_marco_5b.xlsx
@@ -421,7 +421,7 @@
         <v>0.03997675152969091</v>
       </c>
       <c r="D2">
-        <v>0.009462037736368336</v>
+        <v>0.01028082797789644</v>
       </c>
       <c r="E2">
         <v>199883757.6484546</v>
@@ -459,7 +459,7 @@
         <v>0.03619588619759224</v>
       </c>
       <c r="D3">
-        <v>0.008737951488815432</v>
+        <v>0.009494083477434414</v>
       </c>
       <c r="E3">
         <v>180979430.9879612</v>
@@ -497,7 +497,7 @@
         <v>0.04493881006046815</v>
       </c>
       <c r="D4">
-        <v>0.01177716163986146</v>
+        <v>0.01279628936818933</v>
       </c>
       <c r="E4">
         <v>224694050.3023407</v>
@@ -535,7 +535,7 @@
         <v>0.03550998362496413</v>
       </c>
       <c r="D5">
-        <v>0.009931589385983115</v>
+        <v>0.01079101192251045</v>
       </c>
       <c r="E5">
         <v>177549918.1248206</v>
@@ -573,7 +573,7 @@
         <v>0.01470567515443555</v>
       </c>
       <c r="D6">
-        <v>0.004553766125902149</v>
+        <v>0.004947822815378109</v>
       </c>
       <c r="E6">
         <v>73528375.77217777</v>
@@ -611,7 +611,7 @@
         <v>0.03440060917127755</v>
       </c>
       <c r="D7">
-        <v>0.01159672785033151</v>
+        <v>0.01260024187786624</v>
       </c>
       <c r="E7">
         <v>172003045.8563877</v>
@@ -649,7 +649,7 @@
         <v>0.07049848664210395</v>
       </c>
       <c r="D8">
-        <v>0.02751628312381678</v>
+        <v>0.0298973837633026</v>
       </c>
       <c r="E8">
         <v>352492433.2105198</v>
@@ -687,7 +687,7 @@
         <v>0.02854078087441063</v>
       </c>
       <c r="D9">
-        <v>0.01161802873315282</v>
+        <v>0.01262338601638743</v>
       </c>
       <c r="E9">
         <v>142703904.3720531</v>
@@ -725,7 +725,7 @@
         <v>0.03328667005479251</v>
       </c>
       <c r="D10">
-        <v>0.01571701229793696</v>
+        <v>0.01707707200749242</v>
       </c>
       <c r="E10">
         <v>166433350.2739625</v>
@@ -763,7 +763,7 @@
         <v>0.01278087722546964</v>
       </c>
       <c r="D11">
-        <v>0.00636921002306256</v>
+        <v>0.006920364769897064</v>
       </c>
       <c r="E11">
         <v>63904386.12734821</v>
@@ -801,7 +801,7 @@
         <v>0.021319194803451</v>
       </c>
       <c r="D12">
-        <v>0.01100669738730782</v>
+        <v>0.01195915357732504</v>
       </c>
       <c r="E12">
         <v>106595974.017255</v>
@@ -839,7 +839,7 @@
         <v>0.01564514619986043</v>
       </c>
       <c r="D13">
-        <v>0.008083180710287142</v>
+        <v>0.008782652607408487</v>
       </c>
       <c r="E13">
         <v>78225730.99930216</v>
@@ -877,7 +877,7 @@
         <v>0.04982071041328871</v>
       </c>
       <c r="D14">
-        <v>0.02881846769085695</v>
+        <v>0.03131225188180049</v>
       </c>
       <c r="E14">
         <v>249103552.0664435</v>
@@ -915,7 +915,7 @@
         <v>0.02290605900133662</v>
       </c>
       <c r="D15">
-        <v>0.0142979098963997</v>
+        <v>0.01553516865858189</v>
       </c>
       <c r="E15">
         <v>114530295.0066831</v>
@@ -927,10 +927,10 @@
         <v>176269433.4033169</v>
       </c>
       <c r="H15">
-        <v>153.906382056408</v>
+        <v>153.9063820564081</v>
       </c>
       <c r="I15">
-        <v>253.906382056408</v>
+        <v>253.9063820564081</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>0.05776210461891745</v>
       </c>
       <c r="D16">
-        <v>0.039572892387101</v>
+        <v>0.04299730254254351</v>
       </c>
       <c r="E16">
         <v>288810523.0945873</v>
@@ -991,7 +991,7 @@
         <v>0.01442360309469943</v>
       </c>
       <c r="D17">
-        <v>0.0100100757347336</v>
+        <v>0.01087629002777688</v>
       </c>
       <c r="E17">
         <v>72118015.47349717</v>
@@ -1029,16 +1029,16 @@
         <v>0.04188065349285796</v>
       </c>
       <c r="D18">
-        <v>0.03198106575119201</v>
+        <v>0.03474852296076294</v>
       </c>
       <c r="E18">
         <v>209403267.4642898</v>
       </c>
       <c r="F18">
-        <v>650450681.4</v>
+        <v>650450681.4000001</v>
       </c>
       <c r="G18">
-        <v>441047413.9357102</v>
+        <v>441047413.9357103</v>
       </c>
       <c r="H18">
         <v>210.6210754380533</v>
@@ -1067,7 +1067,7 @@
         <v>0.02476472440077774</v>
       </c>
       <c r="D19">
-        <v>0.01897495393444194</v>
+        <v>0.02061693714649891</v>
       </c>
       <c r="E19">
         <v>123823622.0038887</v>
@@ -1105,7 +1105,7 @@
         <v>0.03106350078710079</v>
       </c>
       <c r="D20">
-        <v>0.02451242399111188</v>
+        <v>0.02663358796438357</v>
       </c>
       <c r="E20">
         <v>155317503.9355039</v>
@@ -1143,7 +1143,7 @@
         <v>0.0768001000600067</v>
       </c>
       <c r="D21">
-        <v>0.06078926855682398</v>
+        <v>0.06604962169329989</v>
       </c>
       <c r="E21">
         <v>384000500.3000335</v>
@@ -1181,7 +1181,7 @@
         <v>0.05427611013661751</v>
       </c>
       <c r="D22">
-        <v>0.04820225648990493</v>
+        <v>0.05237340210707692</v>
       </c>
       <c r="E22">
         <v>271380550.6830875</v>
@@ -1219,7 +1219,7 @@
         <v>0.006306371387863901</v>
       </c>
       <c r="D23">
-        <v>0.006139579074849137</v>
+        <v>0.006670862882168432</v>
       </c>
       <c r="E23">
         <v>31531856.9393195</v>
@@ -1257,7 +1257,7 @@
         <v>0.02852737800077722</v>
       </c>
       <c r="D24">
-        <v>0.02786601120906474</v>
+        <v>0.03027737530250919</v>
       </c>
       <c r="E24">
         <v>142636890.0038861</v>
@@ -1295,7 +1295,7 @@
         <v>0.0146420577822676</v>
       </c>
       <c r="D25">
-        <v>0.01459284475740676</v>
+        <v>0.01585562548354717</v>
       </c>
       <c r="E25">
         <v>73210288.91133799</v>
@@ -1333,7 +1333,7 @@
         <v>0.03138103348631988</v>
       </c>
       <c r="D26">
-        <v>0.03250519911166033</v>
+        <v>0.0353180118030807</v>
       </c>
       <c r="E26">
         <v>156905167.4315994</v>
@@ -1371,7 +1371,7 @@
         <v>0.08227494643576272</v>
       </c>
       <c r="D27">
-        <v>0.1060167598332034</v>
+        <v>0.1151908395408133</v>
       </c>
       <c r="E27">
         <v>411374732.1788136</v>
@@ -1409,7 +1409,7 @@
         <v>0.01471389456597418</v>
       </c>
       <c r="D28">
-        <v>0.01970227664869147</v>
+        <v>0.02140719817884247</v>
       </c>
       <c r="E28">
         <v>73569472.82987092</v>
@@ -1447,7 +1447,7 @@
         <v>0.00780842708567104</v>
       </c>
       <c r="D29">
-        <v>0.01225832459754677</v>
+        <v>0.01331908939658968</v>
       </c>
       <c r="E29">
         <v>39042135.4283552</v>
@@ -1485,7 +1485,7 @@
         <v>0.01518693116727706</v>
       </c>
       <c r="D30">
-        <v>0.02525228864499925</v>
+        <v>0.0274374762435759</v>
       </c>
       <c r="E30">
         <v>75934655.83638531</v>
@@ -1523,7 +1523,7 @@
         <v>0.007949529934269608</v>
       </c>
       <c r="D31">
-        <v>0.0134009148789403</v>
+        <v>0.01456055285927206</v>
       </c>
       <c r="E31">
         <v>39747649.67134804</v>
@@ -1561,7 +1561,7 @@
         <v>0.01196759457375883</v>
       </c>
       <c r="D32">
-        <v>0.03301930574418582</v>
+        <v>0.03587660626217645</v>
       </c>
       <c r="E32">
         <v>59837972.86879415</v>
@@ -1599,7 +1599,7 @@
         <v>0.01774539803593836</v>
       </c>
       <c r="D33">
-        <v>0.2160750929933533</v>
+        <v>0.2347729868836116</v>
       </c>
       <c r="E33">
         <v>88726990.17969181</v>
